--- a/data/trans_dic/P04D$notiene-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P04D$notiene-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda</t>
+          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,31</t>
+          <t>2,45; 6,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,45; 20,23</t>
+          <t>12,33; 20,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,2; 18,79</t>
+          <t>6,14; 18,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 7,15</t>
+          <t>2,92; 7,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,67; 18,08</t>
+          <t>10,65; 17,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,14; 14,91</t>
+          <t>4,27; 14,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,85</t>
+          <t>3,06; 6,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,5; 17,7</t>
+          <t>12,77; 17,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,49; 14,49</t>
+          <t>6,25; 14,22</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,66</t>
+          <t>3,4; 7,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,6; 19,79</t>
+          <t>13,16; 19,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,87; 17,49</t>
+          <t>8,92; 17,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,53</t>
+          <t>1,89; 4,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,09; 20,03</t>
+          <t>14,06; 20,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,41; 53,06</t>
+          <t>10,47; 55,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,49</t>
+          <t>3,23; 5,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,57; 19,12</t>
+          <t>14,67; 19,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,2; 37,62</t>
+          <t>11,14; 38,24</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,0</t>
+          <t>2,83; 6,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,78; 16,43</t>
+          <t>10,75; 16,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,28; 15,67</t>
+          <t>10,0; 15,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,03</t>
+          <t>2,82; 6,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,0; 15,13</t>
+          <t>10,28; 15,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,13; 12,0</t>
+          <t>6,94; 12,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,32</t>
+          <t>3,13; 5,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,11; 14,94</t>
+          <t>11,19; 14,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,04; 13,01</t>
+          <t>9,2; 13,22</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,8</t>
+          <t>2,46; 5,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,7; 19,07</t>
+          <t>13,1; 19,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 12,43</t>
+          <t>3,57; 12,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 6,57</t>
+          <t>2,53; 6,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,74; 16,11</t>
+          <t>10,53; 16,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,17; 14,59</t>
+          <t>10,18; 14,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,6</t>
+          <t>3,0; 5,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,58; 16,94</t>
+          <t>12,43; 16,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,61</t>
+          <t>6,42; 12,47</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,96</t>
+          <t>3,15; 7,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,45; 20,75</t>
+          <t>13,03; 20,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,6; 12,59</t>
+          <t>7,36; 12,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,06</t>
+          <t>3,02; 7,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,56; 19,42</t>
+          <t>12,36; 19,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,21; 13,48</t>
+          <t>9,13; 13,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,3</t>
+          <t>3,44; 6,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,71; 18,52</t>
+          <t>13,57; 18,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,99; 12,24</t>
+          <t>9,09; 12,15</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,62</t>
+          <t>1,28; 5,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,7; 20,57</t>
+          <t>12,5; 20,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,18; 12,37</t>
+          <t>7,1; 12,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,01; 7,24</t>
+          <t>3,01; 7,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,14; 18,52</t>
+          <t>11,71; 19,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,12; 11,65</t>
+          <t>3,02; 11,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,3</t>
+          <t>2,41; 5,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,98; 18,16</t>
+          <t>12,96; 18,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,13; 10,88</t>
+          <t>3,87; 10,81</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,46</t>
+          <t>0,95; 5,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,76; 21,5</t>
+          <t>12,68; 21,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,82; 14,33</t>
+          <t>8,0; 14,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1358,27 +1358,27 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,45; 19,59</t>
+          <t>11,63; 19,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,34; 14,05</t>
+          <t>9,29; 13,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,32</t>
+          <t>3,52; 7,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,19; 19,19</t>
+          <t>12,91; 19,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,4; 13,18</t>
+          <t>9,6; 13,52</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,42; 4,89</t>
+          <t>3,43; 4,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,4; 17,1</t>
+          <t>14,5; 17,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,0; 11,96</t>
+          <t>8,32; 11,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,76; 5,19</t>
+          <t>3,82; 5,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,35; 15,83</t>
+          <t>13,45; 15,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,82; 17,32</t>
+          <t>9,68; 17,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,87; 4,84</t>
+          <t>3,83; 4,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,18; 15,97</t>
+          <t>14,21; 16,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,82; 14,13</t>
+          <t>9,82; 14,18</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda</t>
+          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11345; 28527</t>
+          <t>11096; 27971</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52213; 84872</t>
+          <t>51715; 84110</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24800; 75124</t>
+          <t>24550; 75149</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12418; 30616</t>
+          <t>12507; 30731</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42222; 71565</t>
+          <t>42139; 70722</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12979; 46711</t>
+          <t>13386; 46692</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27293; 51476</t>
+          <t>26955; 53128</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>101871; 144294</t>
+          <t>104065; 144314</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46267; 103317</t>
+          <t>44576; 101391</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25781; 52637</t>
+          <t>23369; 51743</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80311; 116883</t>
+          <t>77712; 115330</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37557; 74065</t>
+          <t>37780; 75138</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11473; 27643</t>
+          <t>11517; 29315</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>79429; 112886</t>
+          <t>79215; 113030</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53125; 270882</t>
+          <t>53471; 281895</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40958; 71286</t>
+          <t>41891; 73923</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>168099; 220700</t>
+          <t>169276; 221565</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>104576; 351400</t>
+          <t>104090; 357172</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18853; 40834</t>
+          <t>19269; 42249</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>72139; 109924</t>
+          <t>71924; 109632</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54822; 83547</t>
+          <t>53277; 83962</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19296; 42768</t>
+          <t>20018; 44057</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>66164; 100037</t>
+          <t>68018; 100754</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42160; 70932</t>
+          <t>41039; 71640</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42462; 73980</t>
+          <t>43542; 74739</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>147862; 198732</t>
+          <t>148849; 197533</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>101648; 146278</t>
+          <t>103373; 148660</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15121; 35470</t>
+          <t>15055; 35314</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82042; 123211</t>
+          <t>84643; 124677</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25327; 110377</t>
+          <t>31676; 107936</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17091; 40429</t>
+          <t>15559; 40107</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>69685; 104579</t>
+          <t>68347; 104234</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72304; 103698</t>
+          <t>72364; 104315</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36465; 68703</t>
+          <t>36782; 69486</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>162891; 219370</t>
+          <t>160935; 213184</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>84989; 201575</t>
+          <t>102588; 199325</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12371; 29870</t>
+          <t>13511; 31567</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>64263; 99188</t>
+          <t>62267; 96483</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42491; 70391</t>
+          <t>41153; 68194</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13524; 31624</t>
+          <t>13505; 33020</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>62425; 96471</t>
+          <t>61434; 94658</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50303; 73577</t>
+          <t>49848; 71548</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29918; 55296</t>
+          <t>30172; 55995</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>133617; 180546</t>
+          <t>132240; 181991</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>99408; 135257</t>
+          <t>100507; 134308</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3126; 14322</t>
+          <t>3953; 15558</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42475; 68786</t>
+          <t>41792; 68375</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26396; 45456</t>
+          <t>26104; 45689</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10662; 25638</t>
+          <t>10652; 25907</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>42077; 69948</t>
+          <t>44244; 72438</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18965; 70763</t>
+          <t>18342; 71596</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16780; 35205</t>
+          <t>16016; 35028</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>92408; 129345</t>
+          <t>92312; 130888</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>40220; 106069</t>
+          <t>37725; 105314</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2800; 13584</t>
+          <t>2359; 13884</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>32800; 55256</t>
+          <t>32593; 54575</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22113; 40525</t>
+          <t>22608; 40535</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17509; 37310</t>
+          <t>17511; 37308</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>45808; 78405</t>
+          <t>46554; 77998</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>39723; 59752</t>
+          <t>39503; 59089</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23596; 46722</t>
+          <t>22435; 45158</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>86683; 126131</t>
+          <t>84832; 126054</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>66586; 93299</t>
+          <t>67952; 95761</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>117068; 167283</t>
+          <t>117374; 166824</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>488903; 580562</t>
+          <t>492038; 577072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>276342; 413108</t>
+          <t>287278; 412953</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>133591; 184342</t>
+          <t>135924; 184531</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>473334; 561205</t>
+          <t>476803; 562513</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>363645; 641776</t>
+          <t>358684; 652698</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>269870; 337742</t>
+          <t>266958; 339684</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>984256; 1108322</t>
+          <t>986040; 1118529</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>703057; 1011512</t>
+          <t>703072; 1014943</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$notiene-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P04D$notiene-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,18</t>
+          <t>2,66; 6,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,33; 20,05</t>
+          <t>12,39; 19,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 18,8</t>
+          <t>7,4; 18,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,18</t>
+          <t>2,76; 6,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,65; 17,87</t>
+          <t>10,98; 17,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 14,91</t>
+          <t>6,04; 15,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,03</t>
+          <t>3,08; 5,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,77; 17,7</t>
+          <t>12,72; 17,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 14,22</t>
+          <t>7,78; 15,51</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 7,53</t>
+          <t>3,68; 7,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,16; 19,53</t>
+          <t>13,12; 19,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,92; 17,74</t>
+          <t>10,4; 18,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,8</t>
+          <t>1,83; 4,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,06; 20,06</t>
+          <t>14,0; 19,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,47; 55,21</t>
+          <t>10,19; 16,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,7</t>
+          <t>3,2; 5,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,67; 19,2</t>
+          <t>14,52; 18,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,14; 38,24</t>
+          <t>11,43; 16,72</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,2</t>
+          <t>2,73; 6,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,75; 16,39</t>
+          <t>10,91; 16,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,0; 15,75</t>
+          <t>11,16; 16,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,21</t>
+          <t>2,72; 6,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,28; 15,23</t>
+          <t>10,31; 15,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 12,12</t>
+          <t>9,74; 13,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,37</t>
+          <t>3,16; 5,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,19; 14,85</t>
+          <t>11,17; 14,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,2; 13,22</t>
+          <t>10,87; 14,53</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,78</t>
+          <t>2,45; 5,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,1; 19,3</t>
+          <t>13,23; 19,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 12,16</t>
+          <t>9,96; 15,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,52</t>
+          <t>2,94; 6,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,53; 16,06</t>
+          <t>10,7; 16,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,18; 14,67</t>
+          <t>11,89; 15,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,67</t>
+          <t>3,15; 5,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,43; 16,46</t>
+          <t>12,56; 16,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,42; 12,47</t>
+          <t>11,58; 14,8</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 7,35</t>
+          <t>3,0; 7,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,03; 20,19</t>
+          <t>13,2; 20,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,36; 12,19</t>
+          <t>8,52; 13,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,37</t>
+          <t>2,78; 7,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,36; 19,05</t>
+          <t>12,44; 19,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,13; 13,1</t>
+          <t>10,11; 14,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,38</t>
+          <t>3,44; 6,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,57; 18,67</t>
+          <t>13,56; 18,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,09; 12,15</t>
+          <t>10,02; 13,3</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,28; 5,02</t>
+          <t>1,23; 4,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,5; 20,45</t>
+          <t>12,56; 20,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,1; 12,43</t>
+          <t>7,75; 13,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,01; 7,32</t>
+          <t>2,81; 7,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,71; 19,18</t>
+          <t>11,63; 18,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,02; 11,79</t>
+          <t>9,13; 13,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,28</t>
+          <t>2,41; 5,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,96; 18,38</t>
+          <t>12,89; 18,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,87; 10,81</t>
+          <t>9,07; 12,64</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,58</t>
+          <t>0,87; 5,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,68; 21,24</t>
+          <t>12,79; 21,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,0; 14,34</t>
+          <t>8,75; 15,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,5; 9,59</t>
+          <t>4,28; 9,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,63; 19,49</t>
+          <t>11,39; 19,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,89</t>
+          <t>10,07; 14,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,08</t>
+          <t>3,43; 7,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,91; 19,18</t>
+          <t>12,96; 18,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,6; 13,52</t>
+          <t>10,25; 14,58</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,43; 4,88</t>
+          <t>3,54; 4,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,5; 17,0</t>
+          <t>14,48; 17,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,32; 11,96</t>
+          <t>11,08; 13,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,82; 5,19</t>
+          <t>3,81; 5,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,45; 15,87</t>
+          <t>13,33; 15,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,68; 17,62</t>
+          <t>11,33; 13,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,83; 4,87</t>
+          <t>3,85; 4,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,21; 16,12</t>
+          <t>14,35; 15,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,82; 14,18</t>
+          <t>11,51; 13,09</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45973</t>
+          <t>49283</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25421</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>71394</t>
+          <t>85265</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11096; 27971</t>
+          <t>12053; 29453</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51715; 84110</t>
+          <t>51953; 82655</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24550; 75149</t>
+          <t>29933; 74772</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12507; 30731</t>
+          <t>11814; 28987</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42139; 70722</t>
+          <t>43453; 70653</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13386; 46692</t>
+          <t>21912; 56190</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26955; 53128</t>
+          <t>27151; 51673</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>104065; 144314</t>
+          <t>103698; 144523</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44576; 101391</t>
+          <t>59694; 118975</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53846</t>
+          <t>68352</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>118963</t>
+          <t>65597</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>172808</t>
+          <t>133950</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23369; 51743</t>
+          <t>25293; 53241</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77712; 115330</t>
+          <t>77480; 117645</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37780; 75138</t>
+          <t>49586; 90475</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11517; 29315</t>
+          <t>11187; 28384</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>79215; 113030</t>
+          <t>78889; 112337</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53471; 281895</t>
+          <t>50920; 82615</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41891; 73923</t>
+          <t>41481; 71326</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>169276; 221565</t>
+          <t>167594; 218928</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>104090; 357172</t>
+          <t>111639; 163340</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68116</t>
+          <t>86053</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57068</t>
+          <t>71990</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>125183</t>
+          <t>158044</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19269; 42249</t>
+          <t>18601; 41596</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>71924; 109632</t>
+          <t>73027; 108699</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53277; 83962</t>
+          <t>68793; 103680</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20018; 44057</t>
+          <t>19299; 42701</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>68018; 100754</t>
+          <t>68210; 100073</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41039; 71640</t>
+          <t>60560; 86753</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43542; 74739</t>
+          <t>43882; 75996</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>148849; 197533</t>
+          <t>148560; 197740</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>103373; 148660</t>
+          <t>134511; 179899</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72234</t>
+          <t>86273</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88810</t>
+          <t>102098</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>161044</t>
+          <t>188371</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15055; 35314</t>
+          <t>14967; 35588</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>84643; 124677</t>
+          <t>85452; 123614</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31676; 107936</t>
+          <t>69806; 105092</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15559; 40107</t>
+          <t>18059; 40659</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68347; 104234</t>
+          <t>69479; 104107</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72364; 104315</t>
+          <t>87378; 117316</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36782; 69486</t>
+          <t>38641; 69291</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>160935; 213184</t>
+          <t>162613; 216347</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>102588; 199325</t>
+          <t>166242; 212507</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55352</t>
+          <t>65133</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60557</t>
+          <t>74843</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>115909</t>
+          <t>139975</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13511; 31567</t>
+          <t>12896; 31125</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>62267; 96483</t>
+          <t>63096; 97932</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41153; 68194</t>
+          <t>51732; 81455</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13505; 33020</t>
+          <t>12431; 31658</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>61434; 94658</t>
+          <t>61806; 94728</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>49848; 71548</t>
+          <t>61341; 87900</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30172; 55995</t>
+          <t>30204; 57204</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>132240; 181991</t>
+          <t>132147; 181869</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>100507; 134308</t>
+          <t>121658; 161479</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35526</t>
+          <t>42077</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43734</t>
+          <t>48891</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>79260</t>
+          <t>90968</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3953; 15558</t>
+          <t>3822; 15223</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41792; 68375</t>
+          <t>41995; 68673</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26104; 45689</t>
+          <t>31490; 53753</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10652; 25907</t>
+          <t>9937; 24996</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>44244; 72438</t>
+          <t>43926; 70654</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18342; 71596</t>
+          <t>39965; 59344</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16016; 35028</t>
+          <t>15978; 35954</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>92312; 130888</t>
+          <t>91802; 130030</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>37725; 105314</t>
+          <t>76586; 106728</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30426</t>
+          <t>37106</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49273</t>
+          <t>56728</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>79699</t>
+          <t>93834</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2359; 13884</t>
+          <t>2176; 13708</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>32593; 54575</t>
+          <t>32879; 54486</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22608; 40535</t>
+          <t>27140; 48427</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17511; 37308</t>
+          <t>16638; 37963</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>46554; 77998</t>
+          <t>45568; 77454</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>39503; 59089</t>
+          <t>46753; 69373</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22435; 45158</t>
+          <t>21868; 44965</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>84832; 126054</t>
+          <t>85198; 123415</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>67952; 95761</t>
+          <t>79393; 112895</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>361472</t>
+          <t>434277</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>443825</t>
+          <t>456129</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>805297</t>
+          <t>890406</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>117374; 166824</t>
+          <t>121144; 170593</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>492038; 577072</t>
+          <t>491481; 577793</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>287278; 412953</t>
+          <t>390405; 476922</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>135924; 184531</t>
+          <t>135416; 186417</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>476803; 562513</t>
+          <t>472346; 560787</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>358684; 652698</t>
+          <t>422255; 496250</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>266958; 339684</t>
+          <t>268301; 339356</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>986040; 1118529</t>
+          <t>995617; 1107542</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>703072; 1014943</t>
+          <t>834312; 949008</t>
         </is>
       </c>
     </row>
